--- a/artfynd/A 28775-2026 artfynd.xlsx
+++ b/artfynd/A 28775-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135447743</v>
       </c>
       <c r="B2" t="n">
-        <v>92721</v>
+        <v>92723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>135447734</v>
       </c>
       <c r="B3" t="n">
-        <v>96113</v>
+        <v>96115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135447735</v>
       </c>
       <c r="B4" t="n">
-        <v>92459</v>
+        <v>92461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135447741</v>
       </c>
       <c r="B5" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>135447744</v>
       </c>
       <c r="B13" t="n">
-        <v>92440</v>
+        <v>92442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28775-2026 artfynd.xlsx
+++ b/artfynd/A 28775-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135447743</v>
       </c>
       <c r="B2" t="n">
-        <v>92723</v>
+        <v>92738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>135447734</v>
       </c>
       <c r="B3" t="n">
-        <v>96115</v>
+        <v>96132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135447735</v>
       </c>
       <c r="B4" t="n">
-        <v>92461</v>
+        <v>92475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135447741</v>
       </c>
       <c r="B5" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135447742</v>
       </c>
       <c r="B6" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135447747</v>
       </c>
       <c r="B7" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>135447746</v>
       </c>
       <c r="B8" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135447733</v>
       </c>
       <c r="B9" t="n">
-        <v>4782</v>
+        <v>4783</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>135447737</v>
       </c>
       <c r="B10" t="n">
-        <v>4782</v>
+        <v>4783</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>135447740</v>
       </c>
       <c r="B11" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>135447745</v>
       </c>
       <c r="B12" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>135447744</v>
       </c>
       <c r="B13" t="n">
-        <v>92442</v>
+        <v>92456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
